--- a/Pricing Logic/modules/uploads/module_4_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_1123.xlsx
@@ -396,7 +396,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>7706</v>
+        <v>3478</v>
       </c>
       <c r="B2">
         <v>2</v>

--- a/Pricing Logic/modules/uploads/module_4_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_1123.xlsx
@@ -396,13 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3478</v>
+        <v>2878</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,13 +396,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>2878</v>
+        <v>7885</v>
       </c>
       <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>7885</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>7</v>
+      <c r="C3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
